--- a/Inputs_EmpresaXTest.xlsx
+++ b/Inputs_EmpresaXTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaizen\Documents\tese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C73B15-8977-48C9-9A00-9E142BFE518D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57ED035-4B02-45DD-BAC7-CCEDD2392DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18819,12 +18819,12 @@
         <v>471</v>
       </c>
       <c r="N18">
-        <f>SUM(N5:N13)</f>
-        <v>48029.32</v>
+        <f>_xlfn.XLOOKUP(K18,Table4[ref_id],Table4[euros])*C18</f>
+        <v>5176</v>
       </c>
       <c r="O18">
-        <f>SUM(O5:O13)</f>
-        <v>8180</v>
+        <f>_xlfn.XLOOKUP(K18,Table4[ref_id],Table4[kg])*C18</f>
+        <v>720</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
@@ -18864,6 +18864,14 @@
       <c r="L19" s="37" t="s">
         <v>471</v>
       </c>
+      <c r="N19">
+        <f>_xlfn.XLOOKUP(K19,Table4[ref_id],Table4[euros])*C19</f>
+        <v>5198</v>
+      </c>
+      <c r="O19">
+        <f>_xlfn.XLOOKUP(K19,Table4[ref_id],Table4[kg])*C19</f>
+        <v>736</v>
+      </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="16" t="s">
@@ -18902,9 +18910,25 @@
       <c r="L20" s="37" t="s">
         <v>471</v>
       </c>
+      <c r="N20">
+        <f>_xlfn.XLOOKUP(K20,Table4[ref_id],Table4[euros])*C20</f>
+        <v>20240</v>
+      </c>
+      <c r="O20">
+        <f>_xlfn.XLOOKUP(K20,Table4[ref_id],Table4[kg])*C20</f>
+        <v>3200</v>
+      </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="I21" s="20"/>
+      <c r="N21">
+        <f>SUM(N5:N20)</f>
+        <v>102374.32</v>
+      </c>
+      <c r="O21">
+        <f>SUM(O5:O20)</f>
+        <v>16256</v>
+      </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22"/>
